--- a/assets/constructions/examples/ctd_tgi_module_holder.xlsx
+++ b/assets/constructions/examples/ctd_tgi_module_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,50 +559,74 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CY25A-X10-032-090</t>
+          <t>GHAIL 25-32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cylindrical shank to arbor with driving screws adaptor</t>
+          <t>CUT-GRIP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAND_QD-X10-M</t>
+          <t>GH_32_ISC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HA-25.4</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COR_DISK_4BOLTS_METRIC:X10</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>ISCAR_GH32</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -612,36 +636,48 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>90</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="P2" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>200</v>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="W2" t="b">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
-      </c>
+          <t>2020 / ISCAR Website</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CY32-X22-040-095</t>
+          <t>CY25A-Y25-050-100</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -656,7 +692,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAND_QD-X22-M</t>
+          <t>SAND_QD-Y25-M</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -666,12 +702,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HA-25.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COR_DISK_4BOLTS_METRIC:X22</t>
+          <t>COR_DISK_4BOLTS_INCH:Y25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -690,12 +726,12 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>25.4</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -705,7 +741,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.698</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -715,6 +751,12 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -793,54 +835,56 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GHAIL 25-32</t>
+          <t>CY25-X10-032-090</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CUT-GRIP</t>
+          <t>Cylindrical shank to arbor with driving screws adaptor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GH_32_ISC</t>
+          <t>SAND_QD-X10-M</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ISO_5609:25</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ISCAR_GH32</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>90</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+          <t>COR_DISK_4BOLTS_METRIC:X10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -850,42 +894,42 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>25</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>200</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>90</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.405</v>
+      </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2020 / ISCAR Website</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CY25-X10-032-090</t>
+          <t>CY32-X22-040-095</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -900,7 +944,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAND_QD-X10-M</t>
+          <t>SAND_QD-X22-M</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -910,12 +954,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COR_DISK_4BOLTS_METRIC:X10</t>
+          <t>COR_DISK_4BOLTS_METRIC:X22</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -934,12 +978,12 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -949,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.405</v>
+        <v>0.698</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -959,6 +1003,12 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
